--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8C6854-13F8-45F5-9156-F08B9F300AB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4189A7-2E35-4000-B855-D842D45C818D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{135BEC48-6A3E-46A8-B27F-61595AD5656A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A038286-EB08-4E73-AB84-AF5D7C05CE3F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84BDC9DF-D911-4A0A-BC04-6FCE86081237}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E59F121F-12CB-4C5A-989B-14F3F4E336DC}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4189A7-2E35-4000-B855-D842D45C818D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16FBDBD8-2E48-4072-97A4-9E2EBA3B6CA1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A038286-EB08-4E73-AB84-AF5D7C05CE3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB5F14-4FFD-44FD-935C-EA18711BD00F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E59F121F-12CB-4C5A-989B-14F3F4E336DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B91AC96-3FFA-416C-95B1-1012DCBE07AB}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16FBDBD8-2E48-4072-97A4-9E2EBA3B6CA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FC0D766-ABE1-4BB3-BD71-04D54FDF0085}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB5F14-4FFD-44FD-935C-EA18711BD00F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A62A3D-7A34-4DFF-862E-06EF6AF71FF4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B91AC96-3FFA-416C-95B1-1012DCBE07AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA689BE-A36A-4788-97FF-0F37B3821A9D}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FC0D766-ABE1-4BB3-BD71-04D54FDF0085}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E8F0EA8-37E6-44B9-9322-7D30E29B8DF3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A62A3D-7A34-4DFF-862E-06EF6AF71FF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94E1021-A5A5-4710-8F8C-B9081F3A5192}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA689BE-A36A-4788-97FF-0F37B3821A9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF936DD0-4F45-40A1-8B49-8A130DECBCA9}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E8F0EA8-37E6-44B9-9322-7D30E29B8DF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2B12D11-B74B-4975-ADE8-7EC6A339063E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94E1021-A5A5-4710-8F8C-B9081F3A5192}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{326BB0B0-F321-4662-A3F0-BD69379A70B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF936DD0-4F45-40A1-8B49-8A130DECBCA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D397DA89-2EFC-4065-B634-76ED8002BB5B}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2B12D11-B74B-4975-ADE8-7EC6A339063E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFA8D66F-DE63-4443-AD63-3060EFC16C9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{326BB0B0-F321-4662-A3F0-BD69379A70B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CF78BDD-36FC-465F-9FB5-8D7969075CDF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D397DA89-2EFC-4065-B634-76ED8002BB5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D9DC95B-4E6A-455C-9834-155C973E3FA9}"/>
 </file>
--- a/tools/test-harness/shots/app-test.xlsx
+++ b/tools/test-harness/shots/app-test.xlsx
@@ -1333,13 +1333,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFA8D66F-DE63-4443-AD63-3060EFC16C9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB92D161-42FA-4E77-B618-2798802F6696}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CF78BDD-36FC-465F-9FB5-8D7969075CDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E053317-0111-475E-A0D4-59D4952BBE00}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D9DC95B-4E6A-455C-9834-155C973E3FA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6037B93-345F-4BA2-9820-1071D4125363}"/>
 </file>